--- a/etf_holdings/2026-08-31_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:01</t>
+          <t>2026-08-31 01:36:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:02</t>
+          <t>2026-08-31 01:36:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:04</t>
+          <t>2026-08-31 01:36:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:05</t>
+          <t>2026-08-31 01:36:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:05</t>
+          <t>2026-08-31 01:36:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:05</t>
+          <t>2026-08-31 01:36:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:05</t>
+          <t>2026-08-31 01:36:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 00:41:05</t>
+          <t>2026-08-31 01:36:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-31_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.6%3360</t>
+          <t>+1.93%3425</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3360</v>
+        <v>3425</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0%5490</t>
+          <t>-0.09%5485</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5490</v>
+        <v>5485</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.65%7200</t>
+          <t>-1.46%7095</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.65%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7200</v>
+        <v>7095</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.93%1110</t>
+          <t>-10%999</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.93%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1110</v>
+        <v>999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+3.1%3985</t>
+          <t>-1.51%3925</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3985</v>
+        <v>3925</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3.39%1830</t>
+          <t>+0.55%1840</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3.39%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.28%14300</t>
+          <t>-0.84%14180</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>14300</v>
+        <v>14180</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.6%6015</t>
+          <t>+1.41%6100</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6015</v>
+        <v>6100</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.11%1490</t>
+          <t>-3.69%1435</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.11%</t>
+          <t>-3.69%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1490</v>
+        <v>1435</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.39%2345</t>
+          <t>-1.71%2305</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.39%</t>
+          <t>-1.71%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2345</v>
+        <v>2305</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.67%2125</t>
+          <t>-4.24%2035</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2125</v>
+        <v>2035</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.25%1240</t>
+          <t>-0.81%1230</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.25%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1240</v>
+        <v>1230</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.64%621</t>
+          <t>-5.96%584</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>-5.96%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>621</v>
+        <v>584</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:47</t>
+          <t>2026-08-31 19:31:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.18%5030</t>
+          <t>+1.99%5130</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5030</v>
+        <v>5130</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+7.57%597</t>
+          <t>-8.71%545</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+7.57%</t>
+          <t>-8.71%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>597</v>
+        <v>545</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+9.71%1130</t>
+          <t>+3.1%1165</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+9.71%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1130</v>
+        <v>1165</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.18%540</t>
+          <t>+0.56%543</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+9.98%2260</t>
+          <t>-3.98%2170</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2260</v>
+        <v>2170</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.48%5785</t>
+          <t>+3.54%5990</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>+3.54%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5785</v>
+        <v>5990</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.89%669</t>
+          <t>+1.2%677</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+2.12%15630</t>
+          <t>+2.78%16065</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>15630</v>
+        <v>16065</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.01%2010</t>
+          <t>-2.49%1960</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2010</v>
+        <v>1960</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.73%480.5</t>
+          <t>+4.06%500</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+4.06%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>480.5</v>
+        <v>500</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.93%3305</t>
+          <t>+6.81%3530</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+6.81%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3305</v>
+        <v>3530</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+5.48%317.5</t>
+          <t>-3.94%305</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+5.48%</t>
+          <t>-3.94%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>317.5</v>
+        <v>305</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.96%1545</t>
+          <t>-9.71%1395</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-9.71%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1545</v>
+        <v>1395</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-3.44%1265</t>
+          <t>-7.11%1175</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>-7.11%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1265</v>
+        <v>1175</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-4.55%1365</t>
+          <t>-1.47%1345</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1365</v>
+        <v>1345</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:49</t>
+          <t>2026-08-31 19:31:25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.15%2540</t>
+          <t>-5.51%2400</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.15%</t>
+          <t>-5.51%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2540</v>
+        <v>2400</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+9.7%130</t>
+          <t>-0.77%129</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+9.7%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+3.13%990</t>
+          <t>-2.12%969</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>990</v>
+        <v>969</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+2.17%7065</t>
+          <t>+8.28%7650</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+8.28%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7065</v>
+        <v>7650</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.55%545</t>
+          <t>-0.92%540</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-3.08%220.5</t>
+          <t>+9.98%242.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>220.5</v>
+        <v>242.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.76%111.5</t>
+          <t>+2.24%114</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>111.5</v>
+        <v>114</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.43%707</t>
+          <t>+3.25%730</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+3.25%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>707</v>
+        <v>730</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+5.96%1510</t>
+          <t>-8.61%1380</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>-8.61%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1510</v>
+        <v>1380</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.72%695</t>
+          <t>-1.73%683</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.34%1470</t>
+          <t>-1.36%1450</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.34%</t>
+          <t>-1.36%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1470</v>
+        <v>1450</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.23%2150</t>
+          <t>+0.7%2165</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2150</v>
+        <v>2165</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.34%294</t>
+          <t>+0.17%294.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.34%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>294</v>
+        <v>294.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.84%412</t>
+          <t>+0.36%413.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>412</v>
+        <v>413.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.4%895</t>
+          <t>+3.58%927</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+3.58%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>895</v>
+        <v>927</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:50</t>
+          <t>2026-08-31 19:31:26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.1%722</t>
+          <t>-0.14%721</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:51</t>
+          <t>2026-08-31 19:31:28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+2.38%6250</t>
+          <t>+0.56%6285</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+2.38%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:51</t>
+          <t>2026-08-31 19:31:28</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3317,17 +3317,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.75%529</t>
+          <t>-2.65%515</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>515</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:51</t>
+          <t>2026-08-31 19:31:28</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3380,17 +3380,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.42%181.5</t>
+          <t>+0.55%182.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>181.5</t>
+          <t>182.5</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:51</t>
+          <t>2026-08-31 19:31:28</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3443,17 +3443,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-4.39%1415</t>
+          <t>+0.71%1425</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:51</t>
+          <t>2026-08-31 19:31:28</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3506,17 +3506,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0%135.5</t>
+          <t>+0.37%136</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">

--- a/etf_holdings/2026-08-31_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:24</t>
+          <t>2026-08-31 22:16:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:25</t>
+          <t>2026-08-31 22:16:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:26</t>
+          <t>2026-08-31 22:16:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:28</t>
+          <t>2026-08-31 22:16:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:28</t>
+          <t>2026-08-31 22:16:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:28</t>
+          <t>2026-08-31 22:16:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:28</t>
+          <t>2026-08-31 22:16:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:28</t>
+          <t>2026-08-31 22:16:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-31_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:07</t>
+          <t>2026-08-31 22:23:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:08</t>
+          <t>2026-08-31 22:23:25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:10</t>
+          <t>2026-08-31 22:23:27</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:11</t>
+          <t>2026-08-31 22:23:28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:11</t>
+          <t>2026-08-31 22:23:28</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:11</t>
+          <t>2026-08-31 22:23:28</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:11</t>
+          <t>2026-08-31 22:23:28</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 22:16:11</t>
+          <t>2026-08-31 22:23:28</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
